--- a/data/trans_orig/IP16A12_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A12_2023-Estudios-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2589</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11043</t>
+          <t>10762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>34,83%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13522</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19854</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28540</t>
+          <t>28308</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>20701</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13785</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26653</t>
+          <t>26055</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22044</t>
+          <t>20599</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43734</t>
+          <t>41597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>101832</t>
+          <t>101779</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>115929</t>
+          <t>116357</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93371</t>
+          <t>93969</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106239</t>
+          <t>106546</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>198769</t>
+          <t>200906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>220459</t>
+          <t>221904</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17067</t>
+          <t>17090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19443</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>17611</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31871</t>
+          <t>32503</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,66%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24575</t>
+          <t>24552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34479</t>
+          <t>34130</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27575</t>
+          <t>27831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39361</t>
+          <t>39671</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56790</t>
+          <t>56158</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71890</t>
+          <t>71050</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14685</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35344</t>
+          <t>35624</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28349</t>
+          <t>27471</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47133</t>
+          <t>46478</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46438</t>
+          <t>45122</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75764</t>
+          <t>75508</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144008</t>
+          <t>143728</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164667</t>
+          <t>164094</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135576</t>
+          <t>136231</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154360</t>
+          <t>155238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>286297</t>
+          <t>286553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>315623</t>
+          <t>316939</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A12_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A12_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4895</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1876</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8287</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>35,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,47%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>59,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3526</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3211</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>9,93%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4977</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2145</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8357</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>31,76%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10762</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9025</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5633</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12044</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>64,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>40,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>86,53%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>14224</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11704</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>93,4%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>76,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6570</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9781</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>90,07%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>67,17%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10690</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7310</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>13522</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>68,24%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>46,66%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>86,31%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>27</t>
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>24915</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20135</t>
+          <t>13810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28308</t>
+          <t>20858</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>88,01%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16865</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11829</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23525</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,63%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,96%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,8%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13127</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6123</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20701</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10,72%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,9%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19231</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26055</t>
+          <t>18500</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>32358</t>
+          <t>29093</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20599</t>
+          <t>21446</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41597</t>
+          <t>37403</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>91047</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>84387</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>96083</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,37%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,2%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>109353</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>101779</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>116357</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>89,28%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>100793</t>
+          <t>82105</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93969</t>
+          <t>75833</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106546</t>
+          <t>86587</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>210145</t>
+          <t>173152</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>200906</t>
+          <t>164842</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>221904</t>
+          <t>180799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>89,4%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>122480</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>122480</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>122480</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>94333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>94333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>94333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>242503</t>
+          <t>202245</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>242503</t>
+          <t>202245</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>242503</t>
+          <t>202245</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11791</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6516</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17853</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>27,02%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>40,9%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11536</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7512</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17090</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>41,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>22550</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17611</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32503</t>
+          <t>29648</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>31855</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25793</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37130</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>72,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>59,1%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,07%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>30106</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24552</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>34130</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>72,3%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>58,96%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>81,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34490</t>
+          <t>29769</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27831</t>
+          <t>24689</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39671</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>64597</t>
+          <t>61623</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56158</t>
+          <t>54525</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71050</t>
+          <t>68618</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>81,52%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43646</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43646</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43646</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47018</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47018</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47018</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>88661</t>
+          <t>84173</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88661</t>
+          <t>84173</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88661</t>
+          <t>84173</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33552</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25608</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>42931</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,48%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25,94%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>25669</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15258</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>35624</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,31%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36735</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46478</t>
+          <t>31555</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>62404</t>
+          <t>57510</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45122</t>
+          <t>47256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75508</t>
+          <t>69490</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>131927</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>122548</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>139871</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>79,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74,06%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>153683</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>143728</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>164094</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>85,69%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,49%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>145974</t>
+          <t>120684</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136231</t>
+          <t>113086</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155238</t>
+          <t>127195</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>299657</t>
+          <t>252610</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>286553</t>
+          <t>240630</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>316939</t>
+          <t>262864</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
